--- a/glossary/glossary_v1.xlsx
+++ b/glossary/glossary_v1.xlsx
@@ -337,7 +337,7 @@
     <t>Cosmic completeness; twelve times nine, and the count kept on a mala or rosary in Hindu and Buddhist practice for a single round of recitation. Ancient astronomers noted it as roughly the number of solar diameters between the Sun and the Earth; it recurs, more as a converging symbol of the individual soul's relation to the whole Cosmic than as a literal measurement, throughout Eastern and Western esoteric number-lore alike. 108 is also the top angle (in degrees) of the golden triangle (hosting the eye).108:  1 for the all or the unity 0 for the neant and 8 is the infinity symbol upwards.</t>
   </si>
   <si>
-    <t>Numerology; Step 12; Freemassonery; Origin: Sacred Numbers</t>
+    <t>Numerology; Step 12; Freemasonry; Origin: Sacred Numbers</t>
   </si>
   <si>
     <t>A and B Elements</t>
@@ -1456,7 +1456,7 @@
     <t>The law of compensation and causality. This means that for every cause we institute, an effect follows. For each sorrow or pain we cause another, we shall suffer in like degree and manner when the lesson to be gained will be most impressive. However, the principle does not exact an eye for an eye. It is not retributive, that is, vengeful; rather, its purpose is to teach a lesson and evolve the understanding. The law works two ways; that is, one may have karmic credit due as well as debt. There is collective as well as individual karma.</t>
   </si>
   <si>
-    <t>Shamanism; Budhism; Rosecroix; Step 8; Origin: Ancestral</t>
+    <t>Shamanism; Buddhism; Rosecroix; Step 8; Origin: Ancestral</t>
   </si>
   <si>
     <t>Keyboard</t>
